--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-11 14:35:56</t>
+          <t>2026-09-14 14:57:38</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-14 14:57:38</t>
+          <t>2026-09-15 14:37:48</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:37:48</t>
+          <t>2026-09-16 14:39:12</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-16 14:39:12</t>
+          <t>2026-09-17 14:36:18</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-17 14:36:18</t>
+          <t>2026-09-18 14:33:56</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-18 14:33:56</t>
+          <t>2026-09-18 19:46:15</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-18 19:46:15</t>
+          <t>2026-09-21 15:01:38</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-21 15:01:38</t>
+          <t>2026-09-22 14:44:06</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-22 14:44:06</t>
+          <t>2026-09-23 14:35:51</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-23 14:35:51</t>
+          <t>2026-09-24 14:41:31</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-24 14:41:31</t>
+          <t>2026-09-25 14:33:09</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-25 14:33:09</t>
+          <t>2026-09-25 20:09:12</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-25 20:09:12</t>
+          <t>2026-09-28 15:31:41</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-28 15:31:41</t>
+          <t>2026-09-29 15:28:48</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-29 15:28:48</t>
+          <t>2026-09-30 15:18:46</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-30 15:18:46</t>
+          <t>2026-10-01 15:42:41</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-01 15:42:41</t>
+          <t>2026-10-02 15:28:46</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-02 15:28:46</t>
+          <t>2026-10-05 15:38:24</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-05 15:38:24</t>
+          <t>2026-10-06 16:03:53</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-06 16:03:53</t>
+          <t>2026-10-07 15:41:17</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-07 15:41:17</t>
+          <t>2026-10-08 15:57:14</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-08 15:57:14</t>
+          <t>2026-10-09 15:57:56</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-09 15:57:56</t>
+          <t>2026-10-12 15:55:41</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-12 15:55:41</t>
+          <t>2026-10-13 16:21:59</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-13 16:21:59</t>
+          <t>2026-10-14 14:38:49</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-14 14:38:49</t>
+          <t>2026-10-15 14:21:37</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-15 14:21:37</t>
+          <t>2026-10-15 20:00:14</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-15 20:00:14</t>
+          <t>2026-10-16 14:18:03</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-16 14:18:03</t>
+          <t>2026-10-16 19:50:36</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-16 19:50:36</t>
+          <t>2026-10-19 14:43:36</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-19 14:43:36</t>
+          <t>2026-10-20 14:30:48</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-20 14:30:48</t>
+          <t>2026-10-20 20:01:51</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-20 20:01:51</t>
+          <t>2026-10-21 14:30:08</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-21 14:30:08</t>
+          <t>2026-10-21 20:16:23</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-21 20:16:23</t>
+          <t>2026-10-22 14:32:12</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-22 14:32:12</t>
+          <t>2026-10-22 20:19:28</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-22 20:19:28</t>
+          <t>2026-10-23 14:26:34</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-23 14:26:34</t>
+          <t>2026-10-23 20:00:06</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-23 20:00:06</t>
+          <t>2026-10-26 14:52:44</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-26 14:52:44</t>
+          <t>2026-10-27 14:46:28</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-27 14:46:28</t>
+          <t>2026-10-28 15:18:28</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-28 15:18:28</t>
+          <t>2026-10-29 15:37:45</t>
         </is>
       </c>
     </row>

--- a/index.xlsx
+++ b/index.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-29 15:37:45</t>
+          <t>2026-10-30 15:41:33</t>
         </is>
       </c>
     </row>
